--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2020_biobio_provincial.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2020_biobio_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:47</t>
+    <t xml:space="preserve">2026-10-05 05:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
